--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/WISCONSIN_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/WISCONSIN_2011.xlsx
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C137">
@@ -5323,7 +5323,7 @@
         <v>87</v>
       </c>
       <c r="D276">
-        <v>0.009596293845136</v>
+        <v>0.009596293845136002</v>
       </c>
     </row>
     <row r="277">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C516">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C816">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C832">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C942">
